--- a/src/attributions/attributions_ig_traj_490.xlsx
+++ b/src/attributions/attributions_ig_traj_490.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.01828873090460883</v>
+        <v>-0.01277319539927706</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2359025011151344</v>
+        <v>0.01686513864017091</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,25 +1580,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.01903437251215643</v>
+        <v>0.003332583572330844</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.04515344192204241</v>
+        <v>-0.01165764006416895</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2211404660193707</v>
+        <v>0.03061862660362032</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.05164757626155641</v>
+        <v>-0.008164653617564641</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1622,52 +1622,52 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04230121861859528</v>
+        <v>0.01597405080617698</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2817136776327186</v>
+        <v>0.01584642768999185</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3013420621185717</v>
+        <v>0.007299817883778758</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1292040943616071</v>
+        <v>0.01106645749771129</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.175474056408178</v>
+        <v>0.004020766742032809</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1838825493206163</v>
+        <v>-0.01284572467241473</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>-0</v>
@@ -1676,91 +1676,91 @@
         <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.08127042708140304</v>
+        <v>0.006024322299084371</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.160404763216504</v>
+        <v>0.01736161793531221</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1424483673222063</v>
+        <v>0.02126932237860735</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.08401290876043693</v>
+        <v>-0.01977801540889031</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.6132064502160478</v>
+        <v>0.07080992600225149</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4765674116136295</v>
+        <v>-0.01341422409705003</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.02373673407987165</v>
+        <v>-0.0139647497710932</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0005382941327962791</v>
+        <v>-0.01033750312180135</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.2042922918368268</v>
+        <v>-0.01182390635019772</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.00898743053952109</v>
+        <v>0.007403985506772387</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.1546166097106339</v>
+        <v>0.02013546595551259</v>
       </c>
       <c r="BN3" t="n">
         <v>-0</v>
@@ -1769,13 +1769,13 @@
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1192646680534388</v>
+        <v>0.02523063340730655</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,37 +1784,37 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.05577038224898993</v>
+        <v>0.0002617646573490348</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.3399903998693154</v>
+        <v>0.05738269334794538</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2039519706890335</v>
+        <v>0.01764574016053154</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.0004172398471449453</v>
+        <v>0.011050689586799</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.1890141526568297</v>
+        <v>-0.02113950470859811</v>
       </c>
       <c r="CF3" t="n">
         <v>-0</v>
@@ -1823,13 +1823,13 @@
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.01384851137068388</v>
+        <v>-0.007364765698416243</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
@@ -1838,49 +1838,49 @@
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.04457182520544636</v>
+        <v>-0.002838752762120038</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.004891592039515519</v>
+        <v>-0.01246961323508231</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.05500634011509204</v>
+        <v>-0.003310550251326447</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
         <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.01206848422856523</v>
+        <v>0.004359283688091448</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.1904604706323115</v>
+        <v>-0.02293254251241065</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.02506282229237371</v>
+        <v>-0.01320943280743754</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
         <v>0</v>
@@ -1892,46 +1892,46 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.007648271757795377</v>
+        <v>-0.003363354587029653</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.1693717289016675</v>
+        <v>-0.03994067371567556</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1007954770223174</v>
+        <v>-0.01749266513849059</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.005606299586866865</v>
+        <v>-0.002336503474242368</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.09510175611154166</v>
+        <v>-0.01015679549916795</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.1297004545699715</v>
+        <v>-0.007635470492789551</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1940,31 +1940,31 @@
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
         <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.04311375832597459</v>
+        <v>0.006754361010072115</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.2588025191514832</v>
+        <v>-0.04053983961129617</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.01957666469623</v>
+        <v>-0.02265855551755245</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
@@ -1973,10 +1973,10 @@
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.03926121461778889</v>
+        <v>0.005485712067547941</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.06534367760911659</v>
+        <v>-0.000433224704467964</v>
       </c>
       <c r="EH3" t="n">
         <v>-0</v>
@@ -1985,67 +1985,67 @@
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.08760158305279549</v>
+        <v>-0.01625206180946907</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.01537343840884913</v>
+        <v>0.003189872010333373</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.1954785806452038</v>
+        <v>-0.001624274210496024</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.0584296302265735</v>
+        <v>-0.009759085175412619</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>-0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.04747363403919799</v>
+        <v>0.008433289766947584</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.2067844635125888</v>
+        <v>-0.03280328362283347</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.04012050701953727</v>
+        <v>-0.01338198560348356</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,10 +2054,10 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.01811562056371898</v>
+        <v>0.01250599379937996</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.05438592271480665</v>
+        <v>0.01925801149583102</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
@@ -2066,10 +2066,10 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.0644778953551944</v>
+        <v>-0.01113946306278035</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2078,61 +2078,61 @@
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.05082595721312466</v>
+        <v>0.03751187777500208</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.177142975723298</v>
+        <v>-0.004519658378135305</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.07044356969058531</v>
+        <v>0.02765898186631761</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0.1012533524389996</v>
+        <v>0.02731269603826793</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.1166231858797934</v>
+        <v>-0.02132603314213898</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2709,265 +2709,265 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2845107654788584</v>
+        <v>0.2528442142703153</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06219762372676896</v>
+        <v>-0.1016606367336881</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007203905896899515</v>
+        <v>-0.05848314202952842</v>
       </c>
       <c r="F5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2187163842555981</v>
+        <v>0.2600168038049343</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1175396920577495</v>
+        <v>-0.2212990095252995</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.03704471702879874</v>
+        <v>-0.1176063023276435</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5" t="n">
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1919302175722226</v>
+        <v>0.1501449212694264</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.006944850789490072</v>
+        <v>-0.0290116750213293</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08121189849922385</v>
+        <v>-0.03514528974138882</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1213931907262871</v>
+        <v>-0.08543216417742554</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.04212051237290138</v>
+        <v>-0.2376550322058142</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.04864338542711315</v>
+        <v>-0.1189341723928306</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0388707009996162</v>
+        <v>0.1706530889825519</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.08926333001520766</v>
+        <v>-0.06990296043280692</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.08276928142722026</v>
+        <v>0.07119018900747374</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5339031897411737</v>
+        <v>0.4977324323730997</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.004150944371353284</v>
+        <v>-0.2312047214838075</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2696910287255107</v>
+        <v>-0.3638497309763385</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.06951861685013697</v>
+        <v>0.08317626045314339</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1223612705092115</v>
+        <v>-0.1264689960016279</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1358677645647863</v>
+        <v>-0.01641557188421216</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.08601358186986115</v>
+        <v>0.006774322128194739</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.263041181214902e-10</v>
+        <v>8.552187411186462e-11</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.2236535328735593</v>
+        <v>0.06425433127860311</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2772936957474423</v>
+        <v>0.4355598944317217</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.00471326740954808</v>
+        <v>-0.1572939904824998</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.09233619628499992</v>
+        <v>-0.08554323035889903</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1491794688623678</v>
+        <v>-0.1701196708363328</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.01107808729925985</v>
+        <v>0.178171193057196</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.03234559056950687</v>
+        <v>0.0135182805041242</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2979,49 +2979,49 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0001265141626395375</v>
+        <v>-0.08849054113053803</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.03364588010845108</v>
+        <v>0.05316997365785368</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.0522650339622388</v>
+        <v>0.02591216036672379</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1418237822496879</v>
+        <v>-0.1812626558578624</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.04775432044294006</v>
+        <v>0.1881436758639403</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.03065412413059839</v>
+        <v>0.02595864062976775</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
@@ -3033,16 +3033,16 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.08917351564829262</v>
+        <v>-0.1977457328837453</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.03026860885479291</v>
+        <v>0.2126037817345739</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.1221740340225505</v>
+        <v>0.02581652769068801</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
@@ -3051,112 +3051,112 @@
         <v>-0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.03405873250319054</v>
+        <v>-0.06862992183296841</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.1612092884140635</v>
+        <v>0.03507321041067157</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.03149335143759297</v>
+        <v>0.06926815094882413</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.09570133028248079</v>
+        <v>0.03198714918158432</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.01044050858683122</v>
+        <v>0.1493732621957053</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.04176243527648466</v>
+        <v>-0.0572254708879952</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.1025741891926277</v>
+        <v>-0.1282756214119391</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.03876238132120384</v>
+        <v>0.1559283984711458</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.05861105132747227</v>
+        <v>0.009645530783882122</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.12075459926677</v>
+        <v>-0.1621762733960723</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.1297275739927988</v>
+        <v>-0.1081544853849455</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.1196978000593516</v>
+        <v>-0.06842613617038491</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,25 +3165,25 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1458140837320871</v>
+        <v>-0.2067106871968919</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.008916469642579375</v>
+        <v>0.2098457589229338</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.02580836888176877</v>
+        <v>-0.009438483573743899</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
         <v>0</v>
@@ -3192,19 +3192,19 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01870575474067282</v>
+        <v>-0.1181983804035383</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.06819274210708218</v>
+        <v>0.09435527292601074</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.00492768699714064</v>
+        <v>-0.03730256927862814</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3213,61 +3213,61 @@
         <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.02298474831564163</v>
+        <v>-0.05289911373802064</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.08975275432870498</v>
+        <v>0.2473508838424573</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.01463693483094296</v>
+        <v>0.3461939386216934</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.01633069239920611</v>
+        <v>-0.1429060265137056</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.0746065731070889</v>
+        <v>0.0623541740045945</v>
       </c>
       <c r="GC5" t="n">
         <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>-0</v>
@@ -3275,19 +3275,19 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.0373702695076597</v>
+        <v>-0.008273109910712841</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1384222401348205</v>
+        <v>0.03249918089700431</v>
       </c>
       <c r="C6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006749299168046351</v>
+        <v>-0.004180436710496797</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3296,16 +3296,16 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.03480690017790723</v>
+        <v>-0.007043309724872189</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1247815779618251</v>
+        <v>0.04478914420259842</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02872326802336209</v>
+        <v>-0.01205831590253308</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02335541357922833</v>
+        <v>0.00720789713071189</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1930885248044412</v>
+        <v>0.008078482099210516</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1321531485718625</v>
+        <v>-0.00611589249909946</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
@@ -3356,37 +3356,37 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.07463849932043692</v>
+        <v>-0.002076343297672155</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1530588786341898</v>
+        <v>-0.00132139219890866</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0005191221985495469</v>
+        <v>-0.00292400373176132</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.02446049768300092</v>
+        <v>-0.004234093397089598</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.08117871269567778</v>
+        <v>0.01975498239243074</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,25 +3395,25 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.09733880333479114</v>
+        <v>0.009249178550767491</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.05888915334394656</v>
+        <v>-0.009657899545710356</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2635055516407347</v>
+        <v>0.05826885965080224</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,25 +3422,25 @@
         <v>-0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.3617850227762561</v>
+        <v>-0.01673105312718414</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.04559504420360828</v>
+        <v>-0.007259964974832108</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.04988160680420532</v>
+        <v>0.008323251477209788</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,25 +3449,25 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1942592393321619</v>
+        <v>-0.00943377558651237</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.03170183039211561</v>
+        <v>-0.006060036047561598</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0674265514253274</v>
+        <v>-0.002315924817079283</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,13 +3476,13 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.03368156147511184</v>
+        <v>0.02314780794875162</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3491,19 +3491,19 @@
         <v>-0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.04848428844923344</v>
+        <v>0.002934634246163239</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2033180072447771</v>
+        <v>0.04475305288481545</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.1602246167021956</v>
+        <v>-0.00363563484347716</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -3512,82 +3512,82 @@
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.01024790437190289</v>
+        <v>0.00813699429793234</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.07415476953206389</v>
+        <v>-0.02284507895882504</v>
       </c>
       <c r="CF6" t="n">
         <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0133051641770896</v>
+        <v>0.001341290022631068</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.01562011977487021</v>
+        <v>9.424884980881147e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.01178167303918708</v>
+        <v>-0.01211491671675983</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.04729565541717344</v>
+        <v>0.003571328037436795</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0.003288173413677523</v>
+        <v>0.004381477650184856</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.07702867086770249</v>
+        <v>-0.02267713038234185</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0219226079483172</v>
+        <v>0.001016534042751483</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB6" t="n">
         <v>0</v>
@@ -3599,37 +3599,37 @@
         <v>0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.007054163391983084</v>
+        <v>-0.002086734419539768</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.1700116987875629</v>
+        <v>-0.02234681153936464</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0670533036639749</v>
+        <v>-0.00543879181985903</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM6" t="n">
         <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>8.070661770364447e-05</v>
+        <v>0.001707512981950788</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.05419137485738477</v>
+        <v>-0.01517494879028945</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
@@ -3638,7 +3638,7 @@
         <v>-0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.04595388922823676</v>
+        <v>-0.0002514592986259646</v>
       </c>
       <c r="DS6" t="n">
         <v>-0</v>
@@ -3647,16 +3647,16 @@
         <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.002559311404233718</v>
+        <v>0.01289527437343849</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.07147917380728135</v>
+        <v>0.01306306039836476</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,25 +3665,25 @@
         <v>0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.02541308260428479</v>
+        <v>0.001164365425554342</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.01305162654729859</v>
+        <v>0.001353972607987836</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.02087901684128059</v>
+        <v>-0.01454460612350846</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.04812402926096337</v>
+        <v>-0.0091115343656383</v>
       </c>
       <c r="EK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
@@ -3707,52 +3707,52 @@
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>-0.02108626937592057</v>
+        <v>0.003088961893450788</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.09425536978482278</v>
+        <v>-0.008518321047208378</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.04185282569972015</v>
+        <v>-0.002821530893934385</v>
       </c>
       <c r="ET6" t="n">
         <v>-0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.005596532992056156</v>
+        <v>0.007079213337806213</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.08594388154956971</v>
+        <v>-0.02554543672646637</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.05825967771850793</v>
+        <v>-0.00194373519623289</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,10 +3761,10 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.03262881125462114</v>
+        <v>-0.001501714252514954</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.04484705630500674</v>
+        <v>-0.01384187483416289</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,10 +3773,10 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.06939794759863004</v>
+        <v>0.009003904410218744</v>
       </c>
       <c r="FL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>-0.0017908547994808</v>
+        <v>0.02559849538384694</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.1386311664838075</v>
+        <v>-0.01255795214887102</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,28 +3800,28 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.1334175647859725</v>
+        <v>0.007241199485790256</v>
       </c>
       <c r="FU6" t="n">
         <v>-0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0.05183036393552847</v>
+        <v>0.01331037744600207</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01420068210319723</v>
+        <v>-0.01580950762613133</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3839,24 +3839,24 @@
         <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3271403061391914</v>
+        <v>0.4016299295202271</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1248586285793077</v>
+        <v>-0.2585182968949486</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04065431770969262</v>
+        <v>-0.1021325310227555</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2564537139245167</v>
+        <v>0.3787379320663325</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.144285651592531</v>
+        <v>-0.4114356095981699</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0862125697804472</v>
+        <v>-0.1818487885398765</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3901,25 +3901,25 @@
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1147139299370418</v>
+        <v>0.1803298081398834</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.009650850696959515</v>
+        <v>-0.01942386208376999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03665813688407687</v>
+        <v>-0.02614900808741995</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -3928,22 +3928,22 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06289030537491838</v>
+        <v>0.02983272428798679</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0007930740320534077</v>
+        <v>-0.1438614760445537</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.03983698607220292</v>
+        <v>-0.01875508983347499</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3952,73 +3952,73 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.05204048007853646</v>
+        <v>0.2408277386269301</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.08803420518699066</v>
+        <v>-0.03489394929129914</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01202401817143808</v>
+        <v>0.2109390495040699</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5730593916403347</v>
+        <v>0.7573876672238929</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.04802863504488626</v>
+        <v>-0.3643491053707304</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1917176336043366</v>
+        <v>-0.2474249272730049</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.04630352367324436</v>
+        <v>-0.03101814558404988</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.08673284096339377</v>
+        <v>-0.0823638368450333</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.2060221738932587</v>
+        <v>-0.05970143614722594</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,31 +4027,31 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03138293339182948</v>
+        <v>-0.09483069391515669</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.09304635511045915</v>
+        <v>0.02013883281039838</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.06879252366070847</v>
+        <v>0.1184076750500348</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,43 +4063,43 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.315741100893625</v>
+        <v>0.5126741064147924</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.001366974780397764</v>
+        <v>-0.2738557711688652</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.06709503448784514</v>
+        <v>-0.06681969907971071</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1202226300704577</v>
+        <v>-0.2567132878352357</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.05767496880428549</v>
+        <v>0.1802927521417609</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.03309140743928312</v>
+        <v>0.03393506224455539</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
@@ -4108,28 +4108,28 @@
         <v>-0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-4.307328749112897e-05</v>
+        <v>-0.1096646310264317</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.0191847912983541</v>
+        <v>0.04434733832472686</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.05166218212514975</v>
+        <v>0.02444604708843257</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4141,46 +4141,46 @@
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1127226017668277</v>
+        <v>-0.2825735250428473</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.07987367991549653</v>
+        <v>0.185519647344128</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.02423033359006111</v>
+        <v>0.06183666711093505</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.07910312724372451</v>
+        <v>-0.3560893539507446</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.1048000069676619</v>
+        <v>0.2468905945613477</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.1531836068567495</v>
+        <v>-0.1268639865044541</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,7 +4189,7 @@
         <v>-0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
         <v>0</v>
@@ -4198,19 +4198,19 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.09376386032510214</v>
+        <v>-0.07105233007234625</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.00635751253149161</v>
+        <v>0.1195334772416548</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.004193807030251498</v>
+        <v>-0.1107315223735709</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,43 +4225,43 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.02763036075328506</v>
+        <v>0.1358939869887321</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.01367052785768682</v>
+        <v>0.1371999585243976</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.001605390806076278</v>
+        <v>-0.02949686817651867</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1218272739221813</v>
+        <v>-0.1861799110954133</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.05431662761378242</v>
+        <v>0.1332078339906624</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.06892755209031257</v>
+        <v>0.09092184451505503</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
@@ -4270,7 +4270,7 @@
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,22 +4279,22 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.08788429775997254</v>
+        <v>-0.2428261325048279</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.1222862233666797</v>
+        <v>0.1268331971239554</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.1092053069292736</v>
+        <v>0.01107216105591999</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,46 +4306,46 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.119682422998096</v>
+        <v>-0.3090132202448017</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.08155064559959493</v>
+        <v>0.2140395445106403</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.04912350068074931</v>
+        <v>0.0270754979971846</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.05139447774688755</v>
+        <v>-0.1338338712998382</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>-0.03172845123394852</v>
+        <v>0.0155271842438679</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.00504251724787808</v>
+        <v>0.05229324919179332</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4354,22 +4354,22 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.03689994850782486</v>
+        <v>-0.2449703224528016</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.123607475396052</v>
+        <v>0.4730953167066864</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.1529840619902277</v>
+        <v>0.06412541542147368</v>
       </c>
       <c r="FU7" t="n">
         <v>-0</v>
@@ -4378,34 +4378,34 @@
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.01729360407288796</v>
+        <v>-0.2043530548734638</v>
       </c>
       <c r="GA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0421860319559845</v>
+        <v>0.07888254572421168</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4413,10 +4413,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1022121515338425</v>
+        <v>0.4217003761290882</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02565300275595857</v>
+        <v>0.006527060606580074</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.05974007281872882</v>
+        <v>-0.2507279378709985</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07471836775093207</v>
+        <v>0.4485535468539598</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,67 +4452,67 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.01891213814119543</v>
+        <v>-0.1447700539768433</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.07123661424099736</v>
+        <v>-0.2854737408988935</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02378063145730062</v>
+        <v>-0.03328649759467989</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.02706901721027812</v>
+        <v>-0.1246398765578391</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.004152507411928811</v>
+        <v>-0.1832157404772554</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.02967063354792045</v>
+        <v>0.2021486276069811</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.01145382911945262</v>
+        <v>-0.08552520248447001</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0211060495682074</v>
+        <v>0.05425786926615843</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4524,19 +4524,19 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01838597003487248</v>
+        <v>0.172804415012847</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.005317487463959227</v>
+        <v>0.02839870981373631</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.05066397714465286</v>
+        <v>-0.1848139013383384</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,37 +4548,37 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.136095797631693</v>
+        <v>0.8492010112043589</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.02037955997630842</v>
+        <v>-0.3033322930068975</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1145977807761564</v>
+        <v>-0.4256934626521195</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.04808266550363511</v>
+        <v>0.09134596871519383</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,25 +4587,25 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.04241194706981607</v>
+        <v>0.01490518232843656</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.02808626376205373</v>
+        <v>-0.1604937917513132</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>-0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.036049629101046</v>
+        <v>0.09213307779055473</v>
       </c>
       <c r="BN8" t="n">
         <v>0</v>
@@ -4614,25 +4614,25 @@
         <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.02074187627095526</v>
+        <v>0.1496599708393359</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01510633004144698</v>
+        <v>0.1307945757512975</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
         <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.07356482283748583</v>
+        <v>0.4189881554197716</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.008465781189323774</v>
+        <v>-0.1493790042443771</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.04508296624945801</v>
+        <v>-0.4105074422088504</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4656,10 +4656,10 @@
         <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.03493827230013454</v>
+        <v>-0.2996129962854953</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
@@ -4668,64 +4668,64 @@
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0007469980803889624</v>
+        <v>-0.02599480246764314</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03383264383676457</v>
+        <v>0.217547123399871</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.005620640146028824</v>
+        <v>-0.1822180564851436</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.0008663650972369387</v>
+        <v>0.04781537092133099</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.00440237314330129</v>
+        <v>0.08521000304357644</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.02874259013770118</v>
+        <v>-0.2810835942237948</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.00144829928934511</v>
+        <v>-0.01909945052551626</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.04012075235647219</v>
+        <v>0.1908271853902875</v>
       </c>
       <c r="DB8" t="n">
         <v>-0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.02581490355210844</v>
+        <v>-0.07554146545382477</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04956291342583917</v>
+        <v>-0.1597094866795293</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.013417206961632</v>
+        <v>0.1994970608420942</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,52 +4761,52 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.00785931848425815</v>
+        <v>-0.1050194331752222</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.02262576802755335</v>
+        <v>-0.0174892015284698</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.01448474238011886</v>
+        <v>0.05237035750518029</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.03164000801249501</v>
+        <v>0.1654987237435005</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01723656553032845</v>
+        <v>-0.002668259275118091</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.01065570255274213</v>
+        <v>0.03742535109228817</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4815,13 +4815,13 @@
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.02518638732742823</v>
+        <v>-0.115185918593985</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
@@ -4830,106 +4830,106 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.008100974669062601</v>
+        <v>-0.09162938101044141</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.02313039114056901</v>
+        <v>0.204788307052981</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.01929183172243237</v>
+        <v>-0.1692889642785222</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>5.467250417202124e-05</v>
+        <v>-0.1652523994153187</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.01539787561228617</v>
+        <v>0.1535545869219522</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03033580395402899</v>
+        <v>-0.3024555293254441</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.004532395992652063</v>
+        <v>-0.07217395770886625</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03715897561026392</v>
+        <v>0.2016793611907937</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02017211456718688</v>
+        <v>-0.1914604638849653</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.0285595810485181</v>
+        <v>0.08688798491253433</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0359571071315603</v>
+        <v>0.214563073430523</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.02703605771578391</v>
+        <v>-0.09046327020578396</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,63 +4938,63 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.008778121699101466</v>
+        <v>0.09870034803699276</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.002667336398471977</v>
+        <v>0.02862415576046333</v>
       </c>
       <c r="FV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02503390743261307</v>
+        <v>-0.1123483600349867</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.02093050256348975</v>
+        <v>0.1291183398801661</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2914355878022115</v>
+        <v>0.4566451238718771</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06986324059028202</v>
+        <v>-0.1749892907443806</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04736367919781653</v>
+        <v>-0.1371976014967387</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5006,22 +5006,22 @@
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2000024499441048</v>
+        <v>0.4152718881727336</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07730976686643345</v>
+        <v>-0.327189349582679</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0649951186339195</v>
+        <v>-0.1997306301786811</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5030,28 +5030,28 @@
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1008758379348151</v>
+        <v>0.1737096466489653</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.03434427998343226</v>
+        <v>0.02453286787132515</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01736750947624226</v>
+        <v>-0.079240748963664</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
@@ -5063,25 +5063,25 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.06302809800793785</v>
+        <v>0.05713052871466844</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.01977179030002366</v>
+        <v>-0.1033713296943976</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.06108249911978699</v>
+        <v>-0.1013684774072584</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5090,73 +5090,73 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.04995010068017144</v>
+        <v>0.2503317417351067</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03719364141751091</v>
+        <v>0.02808007579901867</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.05744388578633239</v>
+        <v>0.07020806454960944</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.452894138633897</v>
+        <v>0.6223805721821667</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.05923518487367048</v>
+        <v>-0.3013707033176572</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0954074903480041</v>
+        <v>-0.3915253752365082</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03996367635571892</v>
+        <v>0.01014987666002307</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.06140920799391621</v>
+        <v>-0.11567324292759</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1547387712313021</v>
+        <v>-0.0545435249526923</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,31 +5165,31 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.07850646582745062</v>
+        <v>-0.005547200495653528</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.08086474092521845</v>
+        <v>0.09644192017865992</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.09255832440645137</v>
+        <v>0.1531295952960791</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,19 +5201,19 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2407008470884359</v>
+        <v>0.5058244155889634</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.02870910611381598</v>
+        <v>-0.236947699298052</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.02141842679228268</v>
+        <v>-0.1423409676444192</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5228,16 +5228,16 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.08944047558936326</v>
+        <v>-0.213653542255738</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.03634941524518669</v>
+        <v>0.217557267409122</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01875104645424024</v>
+        <v>0.04311229907574712</v>
       </c>
       <c r="CI9" t="n">
         <v>-0</v>
@@ -5249,25 +5249,25 @@
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.00812433166414301</v>
+        <v>-0.08702948109945588</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.003516882837197156</v>
+        <v>-0.007507127104987149</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.03851777839740085</v>
+        <v>0.03323578710408009</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5276,55 +5276,55 @@
         <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.08301616259864046</v>
+        <v>-0.2312520168875273</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.05768108395859934</v>
+        <v>0.2244771782984634</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.02346353432201191</v>
+        <v>0.04470558796336103</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.05745383327566245</v>
+        <v>-0.2061539870829609</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.1694286023999195</v>
+        <v>0.1687295298717245</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.008156563766461834</v>
+        <v>-0.05567927569322114</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,19 +5336,19 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.05655749900420884</v>
+        <v>-0.1255618350315101</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.0350441949283623</v>
+        <v>0.1099602471082458</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01543375434819846</v>
+        <v>-0.1425144819965595</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
@@ -5363,22 +5363,22 @@
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.03073102582190534</v>
+        <v>0.07608383542706387</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0258000472795795</v>
+        <v>0.1342092688552557</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.01988243055384641</v>
+        <v>-0.09601192652397385</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
@@ -5390,25 +5390,25 @@
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.07390294321799157</v>
+        <v>-0.1142521676216561</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0.0898314710623687</v>
+        <v>-0.2836300988316139</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.03473973079708602</v>
+        <v>0.03142381449179503</v>
       </c>
       <c r="EK9" t="n">
         <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.07334233383610476</v>
+        <v>-0.199508467282904</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.06741901174085994</v>
+        <v>0.1325276202622848</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02961319093308725</v>
+        <v>-0.03301096845168511</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,73 +5444,73 @@
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.08100454868928819</v>
+        <v>-0.2620875447244835</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.06091006037223581</v>
+        <v>0.2336933426465981</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.02707043629064102</v>
+        <v>0.03084828940467065</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.01226016957717831</v>
+        <v>-0.07716885187757862</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.02255362547447378</v>
+        <v>-0.06289405629100628</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.0270900745503432</v>
+        <v>0.1183835196095988</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.004906091039394857</v>
+        <v>-0.1434726353940325</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.02158815315059875</v>
+        <v>0.3963936887717108</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.04181014295752226</v>
+        <v>0.1881291933382093</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5522,28 +5522,28 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02041684962229273</v>
+        <v>-0.1578399444870324</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.02025958354520696</v>
+        <v>0.05319720782060092</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>-0</v>
@@ -5551,79 +5551,79 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.03086334111837878</v>
+        <v>-0.1173651229590981</v>
       </c>
       <c r="B10" t="n">
         <v>-0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1357468380075654</v>
+        <v>0.07433405221516097</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06062868031396693</v>
+        <v>-0.02055248058425543</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.01528078839777524</v>
+        <v>0.01158913664506879</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.004657485597388065</v>
+        <v>-0.1282850905261374</v>
       </c>
       <c r="K10" t="n">
         <v>-0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06573369000572718</v>
+        <v>0.04254775764957305</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.006333627758820304</v>
+        <v>-0.1250881984426843</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.01598532300335719</v>
+        <v>-0.004856151077533368</v>
       </c>
       <c r="Q10" t="n">
         <v>-0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.03592850096440107</v>
+        <v>0.0740651475821929</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.05856201042332058</v>
+        <v>-0.0266086682839233</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.07009513641274621</v>
+        <v>-0.07896860200924773</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.05651063230235919</v>
+        <v>0.02423666319664061</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -5632,133 +5632,133 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.02674665621734236</v>
+        <v>0.1649663615221524</v>
       </c>
       <c r="AC10" t="n">
         <v>-0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0006165561819430943</v>
+        <v>-0.1666992822036973</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.06530075418996657</v>
+        <v>-0.2835843310108623</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.009959600472939137</v>
+        <v>-0.03765955310395888</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.002405332902300402</v>
+        <v>0.0007442939573891165</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.03322067087021374</v>
+        <v>-0.05893827930785656</v>
       </c>
       <c r="AN10" t="n">
         <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.004135571919849119</v>
+        <v>-0.1681423608919736</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.0067950838650274</v>
+        <v>0.04013403451276298</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.01560604085590907</v>
+        <v>-0.126440241843469</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2154163655979833</v>
+        <v>0.07046772851138217</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.3349323025129132</v>
+        <v>-0.3726596227219049</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.01991713682464336</v>
+        <v>0.07635649480201394</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.06899833434550769</v>
+        <v>-0.006637738239321269</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.0312256468953005</v>
+        <v>-0.06724156084004258</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.09290901732339757</v>
+        <v>0.1927643163314365</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0.003529351730313574</v>
+        <v>-0.07353742920620482</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.003479999212402829</v>
+        <v>0.1011340728117924</v>
       </c>
       <c r="BM10" t="n">
         <v>-0</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.1075748940359745</v>
+        <v>0.1113506395989954</v>
       </c>
       <c r="BO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.01202368971751697</v>
+        <v>0.05057699778727538</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0337193286480492</v>
+        <v>0.02431011780655557</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5767,25 +5767,25 @@
         <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0.01231550735119999</v>
+        <v>-0.01274547244931303</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.08225575707681503</v>
+        <v>0.1007882152275584</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.2270234625079457</v>
+        <v>-0.05113057810777671</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0.03569002067902428</v>
+        <v>0.08680004352837394</v>
       </c>
       <c r="CB10" t="n">
         <v>-0</v>
@@ -5794,268 +5794,268 @@
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.02623215846887517</v>
+        <v>0.04866452081655337</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF10" t="n">
-        <v>-0.04213421650626486</v>
+        <v>0.03395296187072608</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01345935023192609</v>
+        <v>0.06577443410417547</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.01253167716165719</v>
+        <v>0.03315230785408607</v>
       </c>
       <c r="CK10" t="n">
         <v>-0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.01172602798045965</v>
+        <v>-0.04314993431560759</v>
       </c>
       <c r="CN10" t="n">
         <v>0</v>
       </c>
       <c r="CO10" t="n">
-        <v>-0.001432782202506547</v>
+        <v>0.01474731635219136</v>
       </c>
       <c r="CP10" t="n">
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.04738846323444777</v>
+        <v>-0.002597174621647952</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0005746261023657837</v>
+        <v>-0.003668815600595729</v>
       </c>
       <c r="CT10" t="n">
         <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0148795755282053</v>
+        <v>0.06570028699439644</v>
       </c>
       <c r="CW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0.04068887028718456</v>
+        <v>-0.009423069066801223</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.005026581389855301</v>
+        <v>0.02338786500456677</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.01995302483989007</v>
+        <v>0.009604762187646509</v>
       </c>
       <c r="DC10" t="n">
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.03376392986311167</v>
+        <v>0.02677211579434597</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0.05604646218033337</v>
+        <v>-0.02523826313605432</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.02512572934743501</v>
+        <v>0.1634430007479661</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.01990194315046829</v>
+        <v>0.006554635149885094</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
         <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.05703985839198498</v>
+        <v>-0.05920578037830945</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.008188260310028244</v>
+        <v>0.003986151789657827</v>
       </c>
       <c r="DQ10" t="n">
         <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01932843676889928</v>
+        <v>-0.113486329119905</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.03496729288996835</v>
+        <v>-0.08890149251629048</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.00745018770428807</v>
+        <v>0.1346821557438538</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.01285977478045691</v>
+        <v>0.02468681939862374</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.03824205086056721</v>
+        <v>-0.09290287467084318</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0.00619260374356446</v>
+        <v>-0.05361594306085624</v>
       </c>
       <c r="ED10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0.003564872081193393</v>
+        <v>-0.01052528251582243</v>
       </c>
       <c r="EG10" t="n">
         <v>0</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0.08654273966764373</v>
+        <v>0.008939499461833587</v>
       </c>
       <c r="EI10" t="n">
         <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01006736144492726</v>
+        <v>0.007840592362168865</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0.005139423895391541</v>
+        <v>0.1356149519526409</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.02709818015060125</v>
+        <v>0.1775569435953643</v>
       </c>
       <c r="EP10" t="n">
         <v>0</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0.02918009253443331</v>
+        <v>0.05971692158689964</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.0552399806398924</v>
+        <v>0.04209521102207182</v>
       </c>
       <c r="ET10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0.01952936625840893</v>
+        <v>0.09868571634545904</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0173409045250026</v>
+        <v>0.03876805033285727</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ10" t="n">
-        <v>-0.04210681465471542</v>
+        <v>-0.02509139374016988</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.01683952722178464</v>
+        <v>0.04768030444991914</v>
       </c>
       <c r="FC10" t="n">
         <v>0</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.01779501824412739</v>
+        <v>0.01266344947265219</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.02400316952772287</v>
+        <v>0.2707300834371887</v>
       </c>
       <c r="FH10" t="n">
         <v>-0</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0.009000179465978924</v>
+        <v>-0.02595403318360275</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.01794288645641695</v>
+        <v>0.09271927976841043</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0.04141240268476096</v>
+        <v>-0.028031848020597</v>
       </c>
       <c r="FN10" t="n">
         <v>0</v>
@@ -6064,40 +6064,40 @@
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>-0.005306366357859588</v>
+        <v>0.1635562165557826</v>
       </c>
       <c r="FQ10" t="n">
         <v>0</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.06295909123305286</v>
+        <v>-0.1531171132395967</v>
       </c>
       <c r="FS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.0474996329234036</v>
+        <v>0.04767835826773467</v>
       </c>
       <c r="FU10" t="n">
         <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0.002519897632924533</v>
+        <v>-0.04483889728456186</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0.0261629351278223</v>
+        <v>0.108010109849073</v>
       </c>
       <c r="FZ10" t="n">
         <v>-0</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.02696673373269124</v>
+        <v>0.02070364725625764</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
@@ -6106,16 +6106,16 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0.02511694491201279</v>
+        <v>-0.03124778027773925</v>
       </c>
       <c r="GF10" t="n">
         <v>0</v>
       </c>
       <c r="GG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1097944988056291</v>
+        <v>0.5738901236051652</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02093762444485545</v>
+        <v>-0.0198635147852868</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.06895013942223045</v>
+        <v>-0.2969531570775968</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.08658429961889977</v>
+        <v>0.6543157764928708</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,70 +6159,70 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01332086292876557</v>
+        <v>-0.1806745552774211</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0598673684067033</v>
+        <v>-0.2577278036123049</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01522509612445713</v>
+        <v>0.1264560682107539</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01386746115135591</v>
+        <v>-0.1023021909366911</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01325886517548903</v>
+        <v>-0.1155957767333536</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01698065468598606</v>
+        <v>0.1111364181807504</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01655606355426052</v>
+        <v>-0.2147284127330202</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0133554105440433</v>
+        <v>-0.04968275281705677</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.008732371348820753</v>
+        <v>0.2275334101513888</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.006106891713810333</v>
+        <v>0.0198217916420002</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.04241573869008061</v>
+        <v>-0.2051141603484582</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,37 +6255,37 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.09986092833658361</v>
+        <v>1.036985737260395</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0006423682481677598</v>
+        <v>-0.3462905729077729</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.07540413021089218</v>
+        <v>-0.3165816035293733</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.06149378226141237</v>
+        <v>-0.03951600048404499</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,52 +6294,52 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.03419101506289174</v>
+        <v>-0.0653061363065558</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.04232287922094297</v>
+        <v>-0.2119197011060781</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>-0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0394051384013884</v>
+        <v>0.1731423856518274</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0143353797854996</v>
+        <v>0.1766979690213708</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.009285236152111256</v>
+        <v>0.06595136367971509</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.05292083240395457</v>
+        <v>0.6389167563854679</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.009491437313510183</v>
+        <v>-0.1459944738319988</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.03712357641536285</v>
+        <v>-0.316590238913516</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6363,25 +6363,25 @@
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.02828227658383355</v>
+        <v>-0.2991992888035941</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.001731823683661432</v>
+        <v>0.04198389419049171</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02278483859695817</v>
+        <v>0.1965153887510477</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,46 +6393,46 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.003002913171880829</v>
+        <v>-0.1867836150314625</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0005680093720727954</v>
+        <v>0.09419262938634355</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.004551690212151735</v>
+        <v>0.08409095173549785</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02242697222430126</v>
+        <v>-0.2866411215035243</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.0009915750186827983</v>
+        <v>0.006046211183276333</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0270540504324927</v>
+        <v>0.1857905413296333</v>
       </c>
       <c r="DB11" t="n">
         <v>-0</v>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.01093701439975773</v>
+        <v>-0.05035650550954296</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01098948196108129</v>
+        <v>-0.07668888697438306</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02791694298072734</v>
+        <v>0.02005470851622299</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,25 +6468,25 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.009399250736297391</v>
+        <v>-0.1151218984121012</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.03042914271451878</v>
+        <v>-0.03285453989665943</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.003008071120035352</v>
+        <v>0.1177337365132406</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
@@ -6495,52 +6495,52 @@
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.02823312049691954</v>
+        <v>0.09691775507241548</v>
       </c>
       <c r="DY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ11" t="n">
         <v>0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.009932367861490184</v>
+        <v>-0.01374706537047675</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.0129485351744842</v>
+        <v>-0.07513368390695879</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.01742550158144157</v>
+        <v>-0.07201226575885314</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.007455588785387394</v>
+        <v>-0.1143533868528641</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.009248289153051408</v>
+        <v>0.1171481712675824</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6549,67 +6549,67 @@
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.008693193702365825</v>
+        <v>-0.1858524843996021</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.008323031873037312</v>
+        <v>-0.05369222172987798</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.01844899513821402</v>
+        <v>0.06842465651759483</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02339592474909429</v>
+        <v>-0.319032416550183</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.006728107130028157</v>
+        <v>-0.009186632421404557</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02818889319622977</v>
+        <v>0.1721556692225995</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.002578128928866239</v>
+        <v>-0.2804144741864795</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,13 +6618,13 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.02176887909126025</v>
+        <v>0.1446611357439511</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03100994825920114</v>
+        <v>0.1505152423470378</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
         <v>0</v>
@@ -6633,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.008457826782753815</v>
+        <v>-0.1399741183222755</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,46 +6645,46 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.008945701380717817</v>
+        <v>0.05499036792942182</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.001053673269432918</v>
+        <v>-0.008253151839928537</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.01549910138829148</v>
+        <v>-0.1310614213381237</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.03576470712292852</v>
+        <v>0.004586251878915721</v>
       </c>
       <c r="GE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,19 +6692,19 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3383443405243972</v>
+        <v>0.2843370589057069</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1505921141478772</v>
+        <v>-0.3037433377479419</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1155340187516716</v>
+        <v>0.02292064452449205</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6713,22 +6713,22 @@
         <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3066728729800095</v>
+        <v>0.3256265048417927</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1173046619446357</v>
+        <v>-0.3034386245368852</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1302415933612011</v>
+        <v>0.02281081312396628</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,25 +6740,25 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.08885819145904059</v>
+        <v>0.09103640400576028</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01838692296302995</v>
+        <v>-0.03228912367512462</v>
       </c>
       <c r="W12" t="n">
-        <v>0.09415142377217792</v>
+        <v>-0.1866422349142943</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,25 +6770,25 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1484901053989108</v>
+        <v>-0.00422844023494357</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.01128518962678167</v>
+        <v>-0.1483513240323278</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.01450723388530666</v>
+        <v>-0.1255771095651024</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
@@ -6797,46 +6797,46 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.01519318366141694</v>
+        <v>0.1597349615643745</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.06222693325943632</v>
+        <v>-0.07345567457092415</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.09324359993508043</v>
+        <v>0.04336106208369109</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4627236986800072</v>
+        <v>0.3950321130013201</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.04563353365331899</v>
+        <v>-0.1308450252973675</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.02023591216234698</v>
+        <v>-0.3035806616041938</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6851,19 +6851,19 @@
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.06574489792983257</v>
+        <v>-0.08478301184500428</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.06780758097916388</v>
+        <v>-0.09251321622710429</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1025403724065054</v>
+        <v>-0.08146584995238874</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6881,16 +6881,16 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1232012818008523</v>
+        <v>0.002686346852633567</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.06552817040503883</v>
+        <v>0.09798772967894633</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1427478649561261</v>
+        <v>0.05866009341817481</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2763345974189239</v>
+        <v>0.2993027112797411</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.0307117811375514</v>
+        <v>-0.1512033766863409</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.07348777372219852</v>
+        <v>-0.09246201313402173</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.0906046108478252</v>
+        <v>-0.1548083280409569</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.02420751220147819</v>
+        <v>0.2121473112133031</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.01924390938378543</v>
+        <v>0.02720475435802436</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,52 +6962,52 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.05467895913892484</v>
+        <v>-0.02751911035553772</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.04856238429323619</v>
+        <v>0.3212740453858741</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06199016587200314</v>
+        <v>0.0977196595563679</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.07745139893089138</v>
+        <v>-0.1340538852130376</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.04052651410928596</v>
+        <v>0.2220030840478792</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.01185569518692343</v>
+        <v>0.03133568337508492</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,43 +7016,43 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.006748183583846532</v>
+        <v>0.01411315845718039</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.1241619162828152</v>
+        <v>0.07984656543665862</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.008626499400173885</v>
+        <v>-0.03242976195692081</v>
       </c>
       <c r="DJ12" t="n">
         <v>0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.08042244526726273</v>
+        <v>-0.1321444141161263</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.06703847540191057</v>
+        <v>0.16747467831105</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.0866073599479657</v>
+        <v>0.009870178487471735</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
@@ -7064,22 +7064,22 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.1153973068997162</v>
+        <v>-0.1107616024142232</v>
       </c>
       <c r="DY12" t="n">
         <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.02000673285354602</v>
+        <v>-0.1081050526182352</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.05628277720393418</v>
+        <v>-0.181634072840552</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
@@ -7088,34 +7088,34 @@
         <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.08699470789034841</v>
+        <v>-0.05621428837160812</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.07819054115150316</v>
+        <v>0.1361693488340511</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.1267367636414899</v>
+        <v>0.04817351713292038</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,25 +7124,25 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.06488676253561834</v>
+        <v>-0.1139977207056184</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03603250621704569</v>
+        <v>0.1365667816966553</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.07523080342250033</v>
+        <v>-0.0348687422854694</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,16 +7151,16 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.07787644460483426</v>
+        <v>-0.1560744042019051</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.04600623410447618</v>
+        <v>0.2303933305063848</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.02808985923135017</v>
+        <v>0.008360287739959419</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,52 +7169,52 @@
         <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.1134464479910015</v>
+        <v>-0.07241218954234717</v>
       </c>
       <c r="FI12" t="n">
         <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.05769299282695068</v>
+        <v>0.1014112830441577</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.06666336431957523</v>
+        <v>-0.2104300625416306</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.01644431841158716</v>
+        <v>-0.03147046960172264</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.02771690791957739</v>
+        <v>-0.0330553604331626</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.05309643694535925</v>
+        <v>0.09155102258660666</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
@@ -7229,16 +7229,16 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.05068129983594179</v>
+        <v>-0.105035495953188</v>
       </c>
       <c r="GA12" t="n">
         <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.01732920456701577</v>
+        <v>0.2150520149439369</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
@@ -7250,7 +7250,7 @@
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
         <v>-0</v>
@@ -7258,34 +7258,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1274105081172724</v>
+        <v>0.119106604325581</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" t="n">
         <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.09921172731217243</v>
+        <v>-0.2588922148307937</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1007893604557608</v>
+        <v>0.0691993719220144</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1302787597856077</v>
+        <v>0.09656251779274952</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -7294,25 +7294,25 @@
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.03730910206144751</v>
+        <v>-0.3119810561330957</v>
       </c>
       <c r="N13" t="n">
-        <v>0.04637360139756862</v>
+        <v>0.007778692754736394</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0247996049666238</v>
+        <v>-0.02559203413907064</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -7321,40 +7321,40 @@
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.05977521739887892</v>
+        <v>-0.06601532017365282</v>
       </c>
       <c r="W13" t="n">
-        <v>0.04768670488093518</v>
+        <v>-0.055967498137423</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>-0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.01852085957725397</v>
+        <v>0.02904573961386028</v>
       </c>
       <c r="AC13" t="n">
         <v>-0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.01871132795936208</v>
+        <v>0.07299201197020339</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.04216951160721504</v>
+        <v>0.2287623409238794</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -7363,49 +7363,49 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.01347344147126953</v>
+        <v>0.02096817930759273</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.02018367403079253</v>
+        <v>-0.1876316459905757</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.06810611634096259</v>
+        <v>0.08382751856843366</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>-0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.09721437060501825</v>
+        <v>-0.0748253929121179</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.07575094777099746</v>
+        <v>-0.3961261376734601</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.1587530121051314</v>
+        <v>-0.01212322578635378</v>
       </c>
       <c r="AY13" t="n">
         <v>-0</v>
@@ -7420,7 +7420,7 @@
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.1032721221389917</v>
+        <v>0.1613750692909476</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -7429,37 +7429,37 @@
         <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.00888506747563037</v>
+        <v>0.2460760384616144</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0701353349805607</v>
+        <v>0.1546281874931391</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.05070689276073196</v>
+        <v>0.003813117454322032</v>
       </c>
       <c r="BM13" t="n">
         <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.01641265501799957</v>
+        <v>0.01247594109246341</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1044615937544579</v>
+        <v>-0.1179006975502009</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
@@ -7468,40 +7468,40 @@
         <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.05050308571970946</v>
+        <v>-0.07989266932078012</v>
       </c>
       <c r="BV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0.01047944185756216</v>
+        <v>-0.3181404602414659</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.08298591883400638</v>
+        <v>-0.04579252694161192</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>0</v>
       </c>
       <c r="CB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0.02788722047748494</v>
+        <v>-0.05706245585713163</v>
       </c>
       <c r="CE13" t="n">
         <v>0</v>
@@ -7510,10 +7510,10 @@
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0.01299306659463535</v>
+        <v>0.1261078068780819</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.02769922872738519</v>
+        <v>-0.02139783643790253</v>
       </c>
       <c r="CI13" t="n">
         <v>0</v>
@@ -7525,37 +7525,37 @@
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-0.01936828525116053</v>
+        <v>0.009130837304713063</v>
       </c>
       <c r="CN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.05141081010287865</v>
+        <v>0.09554151196738975</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.04738197198998675</v>
+        <v>-0.04143216349017871</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0.01735213922875472</v>
+        <v>-0.04692898048878287</v>
       </c>
       <c r="CW13" t="n">
         <v>-0</v>
@@ -7564,10 +7564,10 @@
         <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0009267408852489555</v>
+        <v>0.1239634974524011</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.01824293895837805</v>
+        <v>0.001096598117845166</v>
       </c>
       <c r="DA13" t="n">
         <v>-0</v>
@@ -7579,10 +7579,10 @@
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0.01330178546301631</v>
+        <v>-0.004169370328167164</v>
       </c>
       <c r="DF13" t="n">
         <v>-0</v>
@@ -7591,10 +7591,10 @@
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.07578372508899291</v>
+        <v>0.09588004113033222</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.03497142387663174</v>
+        <v>-0.02286482823406602</v>
       </c>
       <c r="DJ13" t="n">
         <v>0</v>
@@ -7606,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0.02322830444796386</v>
+        <v>-0.06991171994750708</v>
       </c>
       <c r="DO13" t="n">
         <v>-0</v>
@@ -7618,94 +7618,94 @@
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.04093374168895925</v>
+        <v>-0.01396544732022459</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.06672453508734329</v>
+        <v>0.02232396171996119</v>
       </c>
       <c r="DS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0.03309153563836304</v>
+        <v>0.02605564510745069</v>
       </c>
       <c r="DX13" t="n">
         <v>-0</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.02603474053528315</v>
+        <v>0.02959944889519883</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.02166553496663431</v>
+        <v>0.01765838542884414</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>-0.01617213704917918</v>
+        <v>-0.0789939374408319</v>
       </c>
       <c r="EG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01836038796581111</v>
+        <v>0.09514996483524697</v>
       </c>
       <c r="EJ13" t="n">
-        <v>-0.005579505243848418</v>
+        <v>0.04517218913551868</v>
       </c>
       <c r="EK13" t="n">
         <v>0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO13" t="n">
-        <v>-0.0115898130128312</v>
+        <v>0.04089130157282954</v>
       </c>
       <c r="EP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.02220492024859829</v>
+        <v>0.1218243704214452</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01320430470978085</v>
+        <v>0.004314930673304873</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7717,19 +7717,19 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0.01802046526578398</v>
+        <v>-0.05273168257956194</v>
       </c>
       <c r="EY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0.006617917298961641</v>
+        <v>0.1665887470274054</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.02527579663017472</v>
+        <v>-0.01697562214757295</v>
       </c>
       <c r="FC13" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0.01475778016365977</v>
+        <v>0.05507885823117926</v>
       </c>
       <c r="FH13" t="n">
         <v>0</v>
@@ -7753,25 +7753,25 @@
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.03061832585381027</v>
+        <v>0.108384088759285</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.1031396213704524</v>
+        <v>0.1444799158647086</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO13" t="n">
         <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.005702482928402975</v>
+        <v>0.004035618915944237</v>
       </c>
       <c r="FQ13" t="n">
         <v>-0</v>
@@ -7780,40 +7780,40 @@
         <v>-0</v>
       </c>
       <c r="FS13" t="n">
-        <v>-0.00538569467564255</v>
+        <v>0.2256435692504937</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.05251849715824964</v>
+        <v>0.07457444870741309</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.01583913216176002</v>
+        <v>0.03757132355243439</v>
       </c>
       <c r="FZ13" t="n">
         <v>0</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.01073087389460605</v>
+        <v>0.2357860266403936</v>
       </c>
       <c r="GC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8968,22 +8968,22 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4279231561641801</v>
+        <v>0.2939188841566474</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1589869469382828</v>
+        <v>-0.2096050993674653</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.03660992565160615</v>
+        <v>-0.03930977265735534</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
@@ -8995,16 +8995,16 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2785515514023302</v>
+        <v>0.3102922503725093</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2117245904837028</v>
+        <v>-0.3084632299078136</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04132109131708741</v>
+        <v>-0.1270709448486535</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -9022,76 +9022,76 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1049091428271091</v>
+        <v>0.05930623254144502</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.01446832405444884</v>
+        <v>-0.08436321840105228</v>
       </c>
       <c r="W16" t="n">
-        <v>0.09932689289879507</v>
+        <v>-0.1025596587602476</v>
       </c>
       <c r="X16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.04167995967873333</v>
+        <v>-0.04277491907528964</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.003692373712410086</v>
+        <v>-0.1632054664366957</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.01337010712438213</v>
+        <v>-0.05913252539455142</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.00762882108756358</v>
+        <v>0.1157969822922773</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.06779017628110375</v>
+        <v>-0.1346757694247067</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.05742277807217042</v>
+        <v>0.03928841755514654</v>
       </c>
       <c r="AP16" t="n">
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9103,25 +9103,25 @@
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.397193304397688</v>
+        <v>0.3071871092277548</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.0205385954559788</v>
+        <v>-0.08496730604357783</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.09850396812810494</v>
+        <v>-0.2595197496006715</v>
       </c>
       <c r="AY16" t="n">
         <v>-0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
@@ -9130,25 +9130,25 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.05598126319333698</v>
+        <v>-0.01530499792942524</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.1732124450079039</v>
+        <v>-0.0349223192578266</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1115140338875555</v>
+        <v>-0.01376103989122243</v>
       </c>
       <c r="BH16" t="n">
         <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
@@ -9157,19 +9157,19 @@
         <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.1129161934917709</v>
+        <v>0.03609594191405226</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.0466178222852079</v>
+        <v>0.0470771031862718</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.1676713820224182</v>
+        <v>0.05139771796748598</v>
       </c>
       <c r="BQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
         <v>0</v>
@@ -9178,79 +9178,79 @@
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1753781205997937</v>
+        <v>0.1942249485645745</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.0178155021502691</v>
+        <v>-0.1579113756463411</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.06902469514657732</v>
+        <v>-0.08830883548545543</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.09154625162828724</v>
+        <v>-0.09800986833126611</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.001066055415028815</v>
+        <v>0.1253703938253296</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.01504294802723569</v>
+        <v>0.02272813717702731</v>
       </c>
       <c r="CI16" t="n">
         <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.004418613229839737</v>
+        <v>-0.05342781881672947</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.08527387670721977</v>
+        <v>0.190009055064542</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.04920785941687961</v>
+        <v>0.05590423424008576</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9262,19 +9262,19 @@
         <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.06416540034470133</v>
+        <v>-0.094023485328528</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.03200906456610007</v>
+        <v>0.1364293359389348</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.02319549863325032</v>
+        <v>0.03479683676322866</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
@@ -9286,22 +9286,22 @@
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.03773425050010301</v>
+        <v>-0.04485478465090589</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.04195238346698282</v>
+        <v>0.04040101360849777</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0747018921221935</v>
+        <v>-0.1185544738058205</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
@@ -9316,28 +9316,28 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.06326358597731206</v>
+        <v>-0.08654476042757786</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.0200184902200059</v>
+        <v>-0.04818819123102139</v>
       </c>
       <c r="DR16" t="n">
-        <v>-0.04040089330052701</v>
+        <v>0.00587079206010835</v>
       </c>
       <c r="DS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
@@ -9346,19 +9346,19 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.09758314151223167</v>
+        <v>-0.009914472694235815</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0.01487454470074861</v>
+        <v>0.07956434805236391</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.03320343689284713</v>
+        <v>-0.04817624957897033</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
@@ -9367,22 +9367,22 @@
         <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.08055139545154982</v>
+        <v>-0.05885840092462152</v>
       </c>
       <c r="EH16" t="n">
         <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.01058959640830271</v>
+        <v>0.08612157692796762</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.05741514176593135</v>
+        <v>0.05910897130768891</v>
       </c>
       <c r="EK16" t="n">
         <v>0</v>
@@ -9391,31 +9391,31 @@
         <v>-0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.01002762274187602</v>
+        <v>0.01287696631853613</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.01341904244143164</v>
+        <v>0.08009224539214027</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.02359625069369509</v>
+        <v>-0.03095458274618415</v>
       </c>
       <c r="ET16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
@@ -9427,43 +9427,43 @@
         <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.06495968421901568</v>
+        <v>-0.1045490627774828</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>-0.004441123833741585</v>
+        <v>0.1593787836742611</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.008467203535296319</v>
+        <v>0.009376349430355568</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.06264584782729475</v>
+        <v>0.124403335166709</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>-0.007555044852825596</v>
+        <v>0.105041947950116</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.04957299937506342</v>
+        <v>-0.01343857688004109</v>
       </c>
       <c r="FL16" t="n">
         <v>-0</v>
@@ -9472,58 +9472,58 @@
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.05378328263002635</v>
+        <v>0.04352996428824521</v>
       </c>
       <c r="FR16" t="n">
         <v>0</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.01462006557752139</v>
+        <v>0.1614649947167993</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.05027579147419141</v>
+        <v>-0.02420534994942786</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.05742902244926062</v>
+        <v>-0.004125984124420166</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.1164042225091931</v>
+        <v>0.07403619774906947</v>
       </c>
       <c r="GC16" t="n">
         <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
         <v>0</v>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1418150113890258</v>
+        <v>0.2925473138956849</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -9546,25 +9546,25 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.05212934777721806</v>
+        <v>-0.0006604997234588172</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0819161113298854</v>
+        <v>-0.141126492601485</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1192344406435505</v>
+        <v>0.3610406044044477</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9573,10 +9573,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.04095649869977917</v>
+        <v>-0.08114790077522588</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.07582251746744344</v>
+        <v>-0.176018662847695</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -9585,55 +9585,55 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.01196876336721881</v>
+        <v>0.07961436300814562</v>
       </c>
       <c r="U17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.006425497190614597</v>
+        <v>-0.1013749502649836</v>
       </c>
       <c r="X17" t="n">
-        <v>0.01325100171852773</v>
+        <v>-0.007389068436715407</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.007264625703002387</v>
+        <v>-0.02864282605297995</v>
       </c>
       <c r="AD17" t="n">
         <v>-0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.01855019913688282</v>
+        <v>-0.1835729358829446</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.007039344354325801</v>
+        <v>0.02762268508308182</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
@@ -9645,34 +9645,34 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.007700401095348656</v>
+        <v>0.02740239893373322</v>
       </c>
       <c r="AM17" t="n">
         <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01288604712207817</v>
+        <v>-0.02884999842872245</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.01279047310911076</v>
+        <v>0.0007866684706399864</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.1046812517455351</v>
+        <v>0.2997618682648836</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
@@ -9681,25 +9681,25 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.01851524363540282</v>
+        <v>-0.2249486635873681</v>
       </c>
       <c r="AY17" t="n">
-        <v>-0.02489005858091989</v>
+        <v>-0.09076505601574504</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA17" t="n">
         <v>-0</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.04377291656431273</v>
+        <v>-0.0005905598912101266</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
@@ -9708,40 +9708,40 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.05406654001002854</v>
+        <v>-0.007191091550717709</v>
       </c>
       <c r="BH17" t="n">
-        <v>-0.06265376379386371</v>
+        <v>-0.07313500164325319</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.03975849246775683</v>
+        <v>0.03890167081070444</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.02070067695915725</v>
+        <v>0.07023574808382337</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.02039069701765887</v>
+        <v>-0.008477851550275669</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
@@ -9750,10 +9750,10 @@
         <v>0</v>
       </c>
       <c r="BU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.05136044246798737</v>
+        <v>0.1772179952082789</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -9762,10 +9762,10 @@
         <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>-0.01168273282917597</v>
+        <v>-0.06124025182805251</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0.008076658818782705</v>
+        <v>-0.1023478164554745</v>
       </c>
       <c r="CA17" t="n">
         <v>-0</v>
@@ -9774,31 +9774,31 @@
         <v>-0</v>
       </c>
       <c r="CC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.0257638648647999</v>
+        <v>-0.08726809214921016</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.003725703995507794</v>
+        <v>0.01600847386458473</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.02222007007704993</v>
+        <v>0.04985145361821269</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL17" t="n">
         <v>0</v>
@@ -9807,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.005663063808694237</v>
+        <v>-0.06356377826359472</v>
       </c>
       <c r="CO17" t="n">
         <v>-0</v>
@@ -9816,43 +9816,43 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.002952023210437925</v>
+        <v>0.1079149426782336</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.01617253273866866</v>
+        <v>0.05819651474099809</v>
       </c>
       <c r="CS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>-0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.01936055904928424</v>
+        <v>-0.09079047412145513</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.005348362761270307</v>
+        <v>0.008396395116826123</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.02076653581258276</v>
+        <v>0.06846214879045207</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD17" t="n">
         <v>0</v>
@@ -9861,19 +9861,19 @@
         <v>-0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.01504997554724089</v>
+        <v>-0.01872280779506634</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.02224854463538814</v>
+        <v>-0.1090698019751407</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.008558497652296524</v>
+        <v>0.05528884835021865</v>
       </c>
       <c r="DK17" t="n">
         <v>-0</v>
@@ -9882,82 +9882,82 @@
         <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.006262142993605922</v>
+        <v>-0.0286471441245943</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
         <v>0</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01764814668146044</v>
+        <v>-0.06339707095336301</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.00670030298383604</v>
+        <v>0.0360758215035295</v>
       </c>
       <c r="DT17" t="n">
         <v>-0</v>
       </c>
       <c r="DU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>-0.0377514139143583</v>
+        <v>0.008239717554057689</v>
       </c>
       <c r="DY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.01755110630002733</v>
+        <v>-0.03476023524951392</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.01059528448898435</v>
+        <v>0.01974661393767715</v>
       </c>
       <c r="EC17" t="n">
         <v>-0</v>
       </c>
       <c r="ED17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.0285969772375216</v>
+        <v>-0.03227884906439711</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.004972922079231677</v>
+        <v>0.005679457537596598</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.01951201754018511</v>
+        <v>0.004202522289365734</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
@@ -9966,22 +9966,22 @@
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.008653519282402045</v>
+        <v>-0.01311508678743446</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.005030109396400284</v>
+        <v>-0.007976787743528654</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.003537903002002638</v>
+        <v>0.08152561578247559</v>
       </c>
       <c r="EU17" t="n">
         <v>0</v>
@@ -9990,40 +9990,40 @@
         <v>0</v>
       </c>
       <c r="EW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.0203501709139148</v>
+        <v>-0.1022007865763472</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.009312422251047356</v>
+        <v>-0.003330043336736445</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.02627371647542371</v>
+        <v>0.04394784372701722</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>-0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.01886967288879681</v>
+        <v>0.1610029764139557</v>
       </c>
       <c r="FI17" t="n">
         <v>0</v>
@@ -10032,16 +10032,16 @@
         <v>-0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.008232934798936815</v>
+        <v>-0.06563198580182787</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.01643699731229806</v>
+        <v>0.1088475766100894</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
         <v>0</v>
@@ -10050,55 +10050,55 @@
         <v>0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.004206610798787966</v>
+        <v>0.05274451540377427</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.0213006684902095</v>
+        <v>-0.08778362347351576</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.01175768887509159</v>
+        <v>-0.02439524107513594</v>
       </c>
       <c r="FV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0007349640975231169</v>
+        <v>-0.0309776968033058</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
         <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.01020212477184129</v>
+        <v>0.06796946970744042</v>
       </c>
       <c r="GE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10106,22 +10106,22 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4797805271022778</v>
+        <v>0.2482469937478071</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1852091826199542</v>
+        <v>-0.2166008339399337</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.06778738270545873</v>
+        <v>-0.05085274047477481</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H18" t="n">
         <v>-0</v>
@@ -10133,16 +10133,16 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3224838527962762</v>
+        <v>0.2803215955290607</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2084002393092479</v>
+        <v>-0.2885214625250923</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.07830193356709939</v>
+        <v>-0.11538140043669</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -10154,82 +10154,82 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1095507658166658</v>
+        <v>0.04573158121079301</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.01625776455020694</v>
+        <v>-0.0560132879357234</v>
       </c>
       <c r="W18" t="n">
-        <v>0.09311023085823629</v>
+        <v>-0.08790195094509848</v>
       </c>
       <c r="X18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.04663299610649835</v>
+        <v>-0.06408823132118698</v>
       </c>
       <c r="AD18" t="n">
         <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.02606072695577923</v>
+        <v>-0.1133792804260067</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.01321364913300729</v>
+        <v>-0.09544164024761505</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.01801374058238342</v>
+        <v>0.1010524316628588</v>
       </c>
       <c r="AM18" t="n">
         <v>-0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.06537906951489766</v>
+        <v>-0.101995314826544</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.05546673716189235</v>
+        <v>0.02371120336789841</v>
       </c>
       <c r="AP18" t="n">
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10241,25 +10241,25 @@
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.4293223750447213</v>
+        <v>0.2357881288261847</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.02192520135728495</v>
+        <v>-0.09574427336185029</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.08956679125250813</v>
+        <v>-0.2390981338504744</v>
       </c>
       <c r="AY18" t="n">
         <v>-0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>-0</v>
@@ -10268,25 +10268,25 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.04104273628811778</v>
+        <v>-0.02050839657776873</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>-0.1886207140115058</v>
+        <v>-0.04405695113151942</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.1235864214280197</v>
+        <v>-0.009735949885674111</v>
       </c>
       <c r="BH18" t="n">
         <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
         <v>0</v>
@@ -10295,19 +10295,19 @@
         <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.1354131166472439</v>
+        <v>0.02697811842614867</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.04544095500204342</v>
+        <v>0.07484545728073118</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.168352055449901</v>
+        <v>0.03635197015057019</v>
       </c>
       <c r="BQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR18" t="n">
         <v>0</v>
@@ -10316,49 +10316,49 @@
         <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.1981215565126227</v>
+        <v>0.1550113295693692</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.0138029648623435</v>
+        <v>-0.1389896247827818</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.06356184395951558</v>
+        <v>-0.0791716968460161</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD18" t="n">
         <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.09379195038677345</v>
+        <v>-0.06395220839405821</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
-        <v>0.008733418295613476</v>
+        <v>0.1206171132401933</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.009780134545292835</v>
+        <v>0.02358388127056904</v>
       </c>
       <c r="CI18" t="n">
         <v>-0</v>
@@ -10370,79 +10370,79 @@
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.01272648288517118</v>
+        <v>-0.02559207788318069</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>-0.07370164531575235</v>
+        <v>0.1657235022364415</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.07117424787767769</v>
+        <v>0.05948325521930394</v>
       </c>
       <c r="CR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS18" t="n">
         <v>-0</v>
       </c>
       <c r="CT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
         <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.06445219164809565</v>
+        <v>-0.06310937357646415</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.04077977417022122</v>
+        <v>0.1296054627363129</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.01888159809260791</v>
+        <v>0.03071224329510754</v>
       </c>
       <c r="DA18" t="n">
         <v>0</v>
       </c>
       <c r="DB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC18" t="n">
         <v>-0</v>
       </c>
       <c r="DD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.04855299175287207</v>
+        <v>-0.05966246861666048</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.04524326199585982</v>
+        <v>0.0220241541492367</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.03123435189189423</v>
+        <v>-0.0337418575600645</v>
       </c>
       <c r="DJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK18" t="n">
         <v>-0</v>
@@ -10454,28 +10454,28 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.05679164838207558</v>
+        <v>-0.05232826888574188</v>
       </c>
       <c r="DP18" t="n">
         <v>0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>0.009947891907231042</v>
+        <v>-0.03565241846216885</v>
       </c>
       <c r="DR18" t="n">
-        <v>-0.04746127824205065</v>
+        <v>0.001964866982827723</v>
       </c>
       <c r="DS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
         <v>0</v>
@@ -10484,19 +10484,19 @@
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>-0.09817146471382365</v>
+        <v>0.02712254874026752</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0.01052330853337616</v>
+        <v>0.06742818928516947</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.04955009235961691</v>
+        <v>-0.06094651220455547</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
@@ -10505,55 +10505,55 @@
         <v>0</v>
       </c>
       <c r="EE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF18" t="n">
         <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.07830053880581145</v>
+        <v>-0.02811056859794352</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.01641333602679758</v>
+        <v>0.08772222291208855</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.06094548667999357</v>
+        <v>0.05175940344993012</v>
       </c>
       <c r="EK18" t="n">
         <v>0</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.002193325195148521</v>
+        <v>0.001359222487517479</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.007714535535193488</v>
+        <v>0.09325983661534359</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.02997228094498673</v>
+        <v>-0.02506921614747175</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV18" t="n">
         <v>0</v>
@@ -10565,22 +10565,22 @@
         <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.06453247484248251</v>
+        <v>-0.06779091173980491</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.006369784534682374</v>
+        <v>0.1514789047727031</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.01325910691278161</v>
+        <v>0.006509082460071152</v>
       </c>
       <c r="FC18" t="n">
         <v>-0</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
@@ -10592,16 +10592,16 @@
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.05272781888620235</v>
+        <v>0.1255516832831165</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0.007992074326585639</v>
+        <v>0.09804239067162829</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.05286821467286446</v>
+        <v>-0.04172101146961714</v>
       </c>
       <c r="FL18" t="n">
         <v>-0</v>
@@ -10610,31 +10610,31 @@
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.043228319813299</v>
+        <v>0.02943614843536784</v>
       </c>
       <c r="FR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.01875773640838895</v>
+        <v>0.1500614262884907</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.0627179700324834</v>
+        <v>-0.04661075417658835</v>
       </c>
       <c r="FU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW18" t="n">
         <v>0</v>
@@ -10643,25 +10643,25 @@
         <v>0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.05432453257358329</v>
+        <v>0.0100929547337886</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>-0.110116341728181</v>
+        <v>0.04503587985808161</v>
       </c>
       <c r="GC18" t="n">
         <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF18" t="n">
         <v>0</v>
@@ -10672,10 +10672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.3915996649459041</v>
+        <v>0.5102262115918758</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10684,10 +10684,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.09072086468595275</v>
+        <v>-0.006766245447887499</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2830721672286869</v>
+        <v>-0.4312697312378784</v>
       </c>
       <c r="G19" t="n">
         <v>-0</v>
@@ -10699,10 +10699,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3528816317886258</v>
+        <v>0.6630281724845497</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -10711,16 +10711,16 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.02483734293724342</v>
+        <v>-0.1431506960218502</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2585680256594056</v>
+        <v>-0.5177786006170643</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -10729,7 +10729,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.04064447962836121</v>
+        <v>0.1450465041964175</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -10738,37 +10738,37 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.06130311767029282</v>
+        <v>-0.1187545358160736</v>
       </c>
       <c r="X19" t="n">
-        <v>7.049077711911252e-05</v>
+        <v>-0.09128684794451336</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB19" t="n">
         <v>-0</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.007899036486356779</v>
+        <v>-0.05786751549276268</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.01368500499271937</v>
+        <v>-0.3001074265240586</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.01526120556275904</v>
+        <v>0.1562253051917037</v>
       </c>
       <c r="AH19" t="n">
         <v>-0</v>
@@ -10783,22 +10783,22 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.05775921626898211</v>
+        <v>0.1059113698012098</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.007485496319355423</v>
+        <v>-0.06697712057587975</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.07375764687103406</v>
+        <v>-0.08974019029748935</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR19" t="n">
         <v>-0</v>
@@ -10807,37 +10807,37 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.2541213184003214</v>
+        <v>0.7733098583919249</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
         <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>-0.05511290217264957</v>
+        <v>-0.3080101204003281</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0.1452949888226114</v>
+        <v>-0.313019219063503</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.09172253198905023</v>
+        <v>-0.1175755493969561</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
@@ -10846,52 +10846,52 @@
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.06623352065693931</v>
+        <v>0.01204318853194076</v>
       </c>
       <c r="BH19" t="n">
-        <v>-0.09082033722312603</v>
+        <v>-0.039312686536397</v>
       </c>
       <c r="BI19" t="n">
         <v>0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.08797427982319929</v>
+        <v>0.2029552122500499</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
         <v>-0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.02147090339613198</v>
+        <v>0.08658635718468999</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.03016701410453274</v>
+        <v>0.09707678152138427</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.1439991914957534</v>
+        <v>0.4180411204425796</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
@@ -10900,91 +10900,91 @@
         <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>-0.05020931203809727</v>
+        <v>-0.05458822018411747</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0.07473641797218669</v>
+        <v>-0.2475579427132454</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
       </c>
       <c r="CB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.06473798834613056</v>
+        <v>-0.1606032994737381</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
         <v>-0</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.006984513341847715</v>
+        <v>0.06025648882217664</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.06565947616930808</v>
+        <v>0.1276916571153235</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.005130152598004254</v>
+        <v>-0.2485877514007108</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.007291953387249714</v>
+        <v>0.1665187365470231</v>
       </c>
       <c r="CR19" t="n">
-        <v>-0.05247531358054943</v>
+        <v>0.02445912260253008</v>
       </c>
       <c r="CS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
         <v>-0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.0558926493629594</v>
+        <v>-0.149259370104606</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
         <v>0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.00379884336141284</v>
+        <v>0.03975168755226383</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.06898881540297949</v>
+        <v>0.1676740923917064</v>
       </c>
       <c r="DB19" t="n">
         <v>0</v>
@@ -10993,25 +10993,25 @@
         <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.06135915175399909</v>
+        <v>-0.1513624093886457</v>
       </c>
       <c r="DG19" t="n">
         <v>0</v>
       </c>
       <c r="DH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.08415556159940454</v>
+        <v>-0.1389562962581418</v>
       </c>
       <c r="DJ19" t="n">
-        <v>-0.001882910752174652</v>
+        <v>0.03638157536833558</v>
       </c>
       <c r="DK19" t="n">
         <v>0</v>
@@ -11020,13 +11020,13 @@
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.02198602906121881</v>
+        <v>-0.05352875522714699</v>
       </c>
       <c r="DP19" t="n">
         <v>0</v>
@@ -11035,160 +11035,160 @@
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.02709105493686355</v>
+        <v>-0.001473616714997993</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.01557499573893865</v>
+        <v>0.1489761392068431</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
       </c>
       <c r="DU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW19" t="n">
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.04577995684550556</v>
+        <v>-0.04662496398318358</v>
       </c>
       <c r="DY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.02446729040975276</v>
+        <v>0.01743836428578572</v>
       </c>
       <c r="EB19" t="n">
-        <v>0.03628187795870894</v>
+        <v>0.001949371353035528</v>
       </c>
       <c r="EC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.0625351846790997</v>
+        <v>-0.04932475428619399</v>
       </c>
       <c r="EH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI19" t="n">
         <v>-0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.01212071641359689</v>
+        <v>-0.005900836916335542</v>
       </c>
       <c r="EK19" t="n">
-        <v>0.07125238700988845</v>
+        <v>0.02832001692035965</v>
       </c>
       <c r="EL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM19" t="n">
         <v>-0</v>
       </c>
       <c r="EN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO19" t="n">
         <v>0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.03925482114581458</v>
+        <v>-0.07466622391049144</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
         <v>-0</v>
       </c>
       <c r="ES19" t="n">
-        <v>-0.02849246186004278</v>
+        <v>-0.07337426672667322</v>
       </c>
       <c r="ET19" t="n">
-        <v>-0.01543461448412817</v>
+        <v>-0.0374706779596977</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
         <v>0</v>
       </c>
       <c r="EW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX19" t="n">
         <v>0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.05526825397540951</v>
+        <v>-0.1889299066450276</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
         <v>-0</v>
       </c>
       <c r="FB19" t="n">
-        <v>-0.002552967613460943</v>
+        <v>0.01001908225771482</v>
       </c>
       <c r="FC19" t="n">
-        <v>0.06744410034248326</v>
+        <v>0.1314301562561891</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>0</v>
       </c>
       <c r="FF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG19" t="n">
         <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.0150882359174045</v>
+        <v>0.1676108957568307</v>
       </c>
       <c r="FI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ19" t="n">
         <v>-0</v>
       </c>
       <c r="FK19" t="n">
-        <v>7.343728946793379e-05</v>
+        <v>-0.0784924012240636</v>
       </c>
       <c r="FL19" t="n">
-        <v>0.04318257916738885</v>
+        <v>0.201792832338408</v>
       </c>
       <c r="FM19" t="n">
         <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
         <v>0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.001735847605024572</v>
+        <v>0.1001835648649801</v>
       </c>
       <c r="FR19" t="n">
         <v>-0</v>
@@ -11197,37 +11197,37 @@
         <v>-0</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.0445592454591066</v>
+        <v>-0.160806151166472</v>
       </c>
       <c r="FU19" t="n">
-        <v>0.03884764812886873</v>
+        <v>-0.1482306912242548</v>
       </c>
       <c r="FV19" t="n">
         <v>-0</v>
       </c>
       <c r="FW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.02345443647110619</v>
+        <v>-0.0118814973036066</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0.03031004375529048</v>
+        <v>0.195938826959501</v>
       </c>
       <c r="GE19" t="n">
         <v>-0</v>
@@ -11236,7 +11236,7 @@
         <v>-0</v>
       </c>
       <c r="GG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -11244,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1459864676925804</v>
+        <v>0.3764316764668916</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -11253,13 +11253,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.04644232604711433</v>
+        <v>-0.1193365755701971</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0833227915646564</v>
+        <v>-0.1275861167472893</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H20" t="n">
         <v>-0</v>
@@ -11268,10 +11268,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1296064731831525</v>
+        <v>0.4660265104146602</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -11280,67 +11280,67 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.03871110240628067</v>
+        <v>-0.2377030551541272</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.07995334038661481</v>
+        <v>-0.1774634238769862</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.01521047641337729</v>
+        <v>0.1031123865755521</v>
       </c>
       <c r="U20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.002830845724631298</v>
+        <v>-0.09214374448560091</v>
       </c>
       <c r="X20" t="n">
-        <v>0.01529460053382572</v>
+        <v>-0.01659208342173435</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.006539045137681568</v>
+        <v>-0.04001125985904525</v>
       </c>
       <c r="AD20" t="n">
         <v>-0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.01102629227921019</v>
+        <v>-0.2137609912400067</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.0001558048595554314</v>
+        <v>0.07524430605794083</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI20" t="n">
         <v>-0</v>
@@ -11352,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.01297094787824033</v>
+        <v>0.03098871310868441</v>
       </c>
       <c r="AM20" t="n">
         <v>-0</v>
@@ -11361,25 +11361,25 @@
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.01178361479959298</v>
+        <v>-0.05298418402097968</v>
       </c>
       <c r="AP20" t="n">
-        <v>-0.009834037136126707</v>
+        <v>0.008961091288581738</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.1005014334273454</v>
+        <v>0.4384166591175006</v>
       </c>
       <c r="AV20" t="n">
         <v>-0</v>
@@ -11388,16 +11388,16 @@
         <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>-0.02505645121621535</v>
+        <v>-0.3010605702108101</v>
       </c>
       <c r="AY20" t="n">
-        <v>-0.03819922045526743</v>
+        <v>-0.1505278527313435</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
         <v>0</v>
@@ -11406,7 +11406,7 @@
         <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.04070445156340922</v>
+        <v>-0.04220262973967508</v>
       </c>
       <c r="BE20" t="n">
         <v>0</v>
@@ -11415,40 +11415,40 @@
         <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>-0.04376064837965007</v>
+        <v>-0.02805089462870606</v>
       </c>
       <c r="BH20" t="n">
-        <v>-0.058763007623939</v>
+        <v>0.007077476069278439</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK20" t="n">
         <v>0</v>
       </c>
       <c r="BL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.04344680260462486</v>
+        <v>0.06924493817754034</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.02865433732548747</v>
+        <v>0.08373332170460707</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.01632526842713121</v>
+        <v>0.006705258651385004</v>
       </c>
       <c r="BR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS20" t="n">
         <v>-0</v>
@@ -11457,10 +11457,10 @@
         <v>0</v>
       </c>
       <c r="BU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.04763348228080407</v>
+        <v>0.2423775006064492</v>
       </c>
       <c r="BW20" t="n">
         <v>0</v>
@@ -11469,10 +11469,10 @@
         <v>0</v>
       </c>
       <c r="BY20" t="n">
-        <v>-0.005637753028236802</v>
+        <v>-0.09034156967456783</v>
       </c>
       <c r="BZ20" t="n">
-        <v>-0.01131348686379291</v>
+        <v>-0.09849030671597903</v>
       </c>
       <c r="CA20" t="n">
         <v>-0</v>
@@ -11484,28 +11484,28 @@
         <v>-0</v>
       </c>
       <c r="CD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE20" t="n">
-        <v>-0.02232693483819628</v>
+        <v>-0.09530612684384594</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG20" t="n">
         <v>-0</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.003714059178834083</v>
+        <v>0.06389409685393108</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.02225706331981295</v>
+        <v>0.04688620324193892</v>
       </c>
       <c r="CJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL20" t="n">
         <v>0</v>
@@ -11514,7 +11514,7 @@
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>-0.01594930237186459</v>
+        <v>-0.140894472294348</v>
       </c>
       <c r="CO20" t="n">
         <v>-0</v>
@@ -11523,148 +11523,148 @@
         <v>-0</v>
       </c>
       <c r="CQ20" t="n">
-        <v>0.009295881439115073</v>
+        <v>0.1961103606830519</v>
       </c>
       <c r="CR20" t="n">
-        <v>-0.004410816959995088</v>
+        <v>0.04299939175098589</v>
       </c>
       <c r="CS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV20" t="n">
         <v>-0</v>
       </c>
       <c r="CW20" t="n">
-        <v>-0.015590898225283</v>
+        <v>-0.09662289316780369</v>
       </c>
       <c r="CX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY20" t="n">
         <v>0</v>
       </c>
       <c r="CZ20" t="n">
-        <v>0.005758420897159645</v>
+        <v>0.05609538089898897</v>
       </c>
       <c r="DA20" t="n">
-        <v>0.02166772380915599</v>
+        <v>0.06851804229554508</v>
       </c>
       <c r="DB20" t="n">
         <v>0</v>
       </c>
       <c r="DC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF20" t="n">
-        <v>-0.03382510995906039</v>
+        <v>-0.03988650318085197</v>
       </c>
       <c r="DG20" t="n">
         <v>-0</v>
       </c>
       <c r="DH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI20" t="n">
-        <v>0.02238230506447435</v>
+        <v>-0.1208265854193372</v>
       </c>
       <c r="DJ20" t="n">
-        <v>-0.0004314575866276734</v>
+        <v>0.02135657672114676</v>
       </c>
       <c r="DK20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>-0.01137881013406565</v>
+        <v>-0.004523598603709998</v>
       </c>
       <c r="DP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>0.00824617705764065</v>
+        <v>-0.05585203043852375</v>
       </c>
       <c r="DS20" t="n">
-        <v>-0.01363273697851866</v>
+        <v>0.01609813161690306</v>
       </c>
       <c r="DT20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX20" t="n">
-        <v>-0.02474049572910414</v>
+        <v>-0.002472692482122132</v>
       </c>
       <c r="DY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ20" t="n">
         <v>-0</v>
       </c>
       <c r="EA20" t="n">
-        <v>0.01455239921255093</v>
+        <v>-0.003355394450046241</v>
       </c>
       <c r="EB20" t="n">
-        <v>0.005100640975322824</v>
+        <v>-0.001509493460055001</v>
       </c>
       <c r="EC20" t="n">
         <v>-0</v>
       </c>
       <c r="ED20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-0.01920193022291034</v>
+        <v>-0.04321942579659008</v>
       </c>
       <c r="EH20" t="n">
         <v>-0</v>
       </c>
       <c r="EI20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.003703542656038597</v>
+        <v>0.04747580571683346</v>
       </c>
       <c r="EK20" t="n">
-        <v>0.01933329720553396</v>
+        <v>0.007534445615905796</v>
       </c>
       <c r="EL20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM20" t="n">
         <v>-0</v>
@@ -11676,79 +11676,79 @@
         <v>0</v>
       </c>
       <c r="EP20" t="n">
-        <v>-0.004827386171694094</v>
+        <v>-0.02368662032265262</v>
       </c>
       <c r="EQ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES20" t="n">
-        <v>0.009454003317658223</v>
+        <v>0.004481991161459833</v>
       </c>
       <c r="ET20" t="n">
-        <v>0.006505189430166875</v>
+        <v>0.07417922774115902</v>
       </c>
       <c r="EU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV20" t="n">
         <v>0</v>
       </c>
       <c r="EW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX20" t="n">
         <v>0</v>
       </c>
       <c r="EY20" t="n">
-        <v>-0.01504456405110235</v>
+        <v>-0.1142908095851968</v>
       </c>
       <c r="EZ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA20" t="n">
         <v>-0</v>
       </c>
       <c r="FB20" t="n">
-        <v>0.007587556470776972</v>
+        <v>0.04317840505877577</v>
       </c>
       <c r="FC20" t="n">
-        <v>0.02633074701446189</v>
+        <v>0.03885835781722507</v>
       </c>
       <c r="FD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE20" t="n">
         <v>-0</v>
       </c>
       <c r="FF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG20" t="n">
         <v>0</v>
       </c>
       <c r="FH20" t="n">
-        <v>-0.01373427251682238</v>
+        <v>0.1613828776524866</v>
       </c>
       <c r="FI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ20" t="n">
         <v>-0</v>
       </c>
       <c r="FK20" t="n">
-        <v>0.008850068795594896</v>
+        <v>-0.1031514966774304</v>
       </c>
       <c r="FL20" t="n">
-        <v>0.01677827084117568</v>
+        <v>0.09731195443751554</v>
       </c>
       <c r="FM20" t="n">
         <v>0</v>
       </c>
       <c r="FN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO20" t="n">
         <v>0</v>
@@ -11757,46 +11757,46 @@
         <v>0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>0.002956938044557995</v>
+        <v>0.07719016502198287</v>
       </c>
       <c r="FR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS20" t="n">
         <v>-0</v>
       </c>
       <c r="FT20" t="n">
-        <v>-0.0208663456707841</v>
+        <v>-0.1514198436556562</v>
       </c>
       <c r="FU20" t="n">
-        <v>0.006382432835950882</v>
+        <v>-0.06307412950728002</v>
       </c>
       <c r="FV20" t="n">
         <v>-0</v>
       </c>
       <c r="FW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>-0.006444098791096322</v>
+        <v>-0.04929187675193637</v>
       </c>
       <c r="GA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB20" t="n">
         <v>-0</v>
       </c>
       <c r="GC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD20" t="n">
-        <v>-0.006334992924899746</v>
+        <v>0.08975867399562142</v>
       </c>
       <c r="GE20" t="n">
         <v>-0</v>
